--- a/baterias_iniciales.xlsx
+++ b/baterias_iniciales.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ce3gk\OneDrive\Escritorio\opti\proyecto\ics1113_proyecto_grupo03\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marti\OneDrive\Documentos\UC\Semester 6\OPTI\tarea\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D577B67C-920E-40B0-B004-0CB76BE67D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E455B49-9F46-466C-8995-720A92A4E373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="b0" sheetId="1" r:id="rId1"/>
@@ -413,9 +413,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -423,7 +423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -431,7 +431,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -447,9 +447,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8348973-3745-4E8A-AACF-B03DAF53BE2B}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,7 +457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -465,7 +465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
